--- a/artfynd/A 25033-2025 artfynd.xlsx
+++ b/artfynd/A 25033-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1062,137 @@
           <t>Trädportalen</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131742125</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>515</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blylav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pectenia plumbea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Berget V Torrsjön, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>332669</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6543141</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håbol</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-05-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-05-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog med stor inslag av löv på gammal åkermark.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Två bålar på grövre asp.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula # Två bålar på grövre asp.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25033-2025 artfynd.xlsx
+++ b/artfynd/A 25033-2025 artfynd.xlsx
@@ -1068,7 +1068,7 @@
         <v>131742125</v>
       </c>
       <c r="B5" t="n">
-        <v>80327</v>
+        <v>80328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25033-2025 artfynd.xlsx
+++ b/artfynd/A 25033-2025 artfynd.xlsx
@@ -1068,7 +1068,7 @@
         <v>131742125</v>
       </c>
       <c r="B5" t="n">
-        <v>80328</v>
+        <v>80331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25033-2025 artfynd.xlsx
+++ b/artfynd/A 25033-2025 artfynd.xlsx
@@ -1068,7 +1068,7 @@
         <v>131742125</v>
       </c>
       <c r="B5" t="n">
-        <v>80331</v>
+        <v>80333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25033-2025 artfynd.xlsx
+++ b/artfynd/A 25033-2025 artfynd.xlsx
@@ -1068,7 +1068,7 @@
         <v>131742125</v>
       </c>
       <c r="B5" t="n">
-        <v>80333</v>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25033-2025 artfynd.xlsx
+++ b/artfynd/A 25033-2025 artfynd.xlsx
@@ -1068,7 +1068,7 @@
         <v>131742125</v>
       </c>
       <c r="B5" t="n">
-        <v>80336</v>
+        <v>80341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25033-2025 artfynd.xlsx
+++ b/artfynd/A 25033-2025 artfynd.xlsx
@@ -1068,7 +1068,7 @@
         <v>131742125</v>
       </c>
       <c r="B5" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25033-2025 artfynd.xlsx
+++ b/artfynd/A 25033-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97215729</v>
+        <v>131742125</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>515</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DALS-ED, Dls</t>
+          <t>Berget V Torrsjön, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332603.8549187264</v>
+        <v>332669</v>
       </c>
       <c r="R2" t="n">
-        <v>6542935.230153611</v>
+        <v>6543141</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,34 +741,14 @@
           <t>Håbol</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1F7C4230-4FAC-48D2-8114-AF5C2D05B53D</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-05-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>{0084AF3D-F653-4F5A-A8EB-E62D7546BF24}</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,37 +757,59 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog med stor inslag av löv på gammal åkermark.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Två bålar på grövre asp.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula # Två bålar på grövre asp.</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Stenström</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Calle Bergil</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>97215699</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332596.8795502685</v>
+        <v>332597</v>
       </c>
       <c r="R3" t="n">
-        <v>6542941.209917416</v>
+        <v>6542941</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,19 +883,9 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -935,15 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97215750</v>
+        <v>97215728</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332603.9905164562</v>
+        <v>332604</v>
       </c>
       <c r="R4" t="n">
-        <v>6542950.186804764</v>
+        <v>6542935</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +990,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>584B67AC-127C-4A55-BA98-77B049CFC97B</t>
+          <t>1F7C4230-4FAC-48D2-8114-AF5C2D05B53D</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1017,24 +998,14 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>{5CC62748-443C-4BC6-B141-69AB28699EDE}</t>
+          <t>{0084AF3D-F653-4F5A-A8EB-E62D7546BF24}</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131742125</v>
+        <v>97215750</v>
       </c>
       <c r="B5" t="n">
-        <v>80384</v>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,40 +1047,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>515</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Berget V Torrsjön, Dls</t>
+          <t>DALS-ED, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>332669</v>
+        <v>332604</v>
       </c>
       <c r="R5" t="n">
-        <v>6543141</v>
+        <v>6542950</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,14 +1103,24 @@
           <t>Håbol</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>584B67AC-127C-4A55-BA98-77B049CFC97B</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2018-05-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2018-05-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>{5CC62748-443C-4BC6-B141-69AB28699EDE}</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,52 +1129,25 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog med stor inslag av löv på gammal åkermark.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Två bålar på grövre asp.</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula # Två bålar på grövre asp.</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Anna Stenström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Calle Bergil</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
